--- a/Abdo_Platooning_Scenario/Autonomous-A.xlsx
+++ b/Abdo_Platooning_Scenario/Autonomous-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ELE_4\Autonomous_A\Truck-Platooning-Group_B\Abdo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ELE_4\Autonomous_A\Truck-Platooning-Group_B\Abdo_Platooning_Scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C2F9C8-65B5-4BBA-B5C0-17871416F5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED90272-75C3-48A8-8850-343C2586A335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>Status</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">Merge intent as (merge_request) - Gap readiness as (gap_ready) -  Timing guarantees as (Clocks (t)) - Safe timing windows as (MAX_*_TIME) </t>
-  </si>
-  <si>
-    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -717,9 +714,7 @@
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="20"/>
-      <c r="E8" s="17" t="s">
-        <v>17</v>
-      </c>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
